--- a/Datos Tesis Upstream/Estructura de Datos/2526-2/Participaciones ESTRUCTURAS DE DATOS - Enero-Marzo 2526-2.xlsx
+++ b/Datos Tesis Upstream/Estructura de Datos/2526-2/Participaciones ESTRUCTURAS DE DATOS - Enero-Marzo 2526-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelsoncarrillo/Downloads/tesis-prediccion-participacion/Datos Tesis Upstream/Estructura de Datos/2526-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D91A3AC-695D-E84D-91A0-5AF8D56AA210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3382A3E8-F32C-514E-8B9D-3E03F5740EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESTRUCTURAS-DE DATOS" sheetId="1" r:id="rId1"/>
@@ -481,7 +481,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{EFF6B67A-3EA1-DF4A-9B38-45B3E7A815A7}">
+    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{EFF6B67A-3EA1-DF4A-9B38-45B3E7A815A7}">
       <text>
         <r>
           <rPr>
@@ -494,7 +494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{8AF044AF-E47D-8B40-9656-616C666C77E5}">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{8AF044AF-E47D-8B40-9656-616C666C77E5}">
       <text>
         <r>
           <rPr>
@@ -507,7 +507,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{EAD118CD-11AE-A94B-9B45-607AF1E180E2}">
+    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{EAD118CD-11AE-A94B-9B45-607AF1E180E2}">
       <text>
         <r>
           <rPr>
@@ -521,7 +521,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P8" authorId="0" shapeId="0" xr:uid="{FC4395AA-3345-5C46-AF99-28E5DD59A749}">
+    <comment ref="Q8" authorId="0" shapeId="0" xr:uid="{FC4395AA-3345-5C46-AF99-28E5DD59A749}">
       <text>
         <r>
           <rPr>
@@ -535,7 +535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA8" authorId="0" shapeId="0" xr:uid="{C81C0957-4AA8-2C44-9B2A-21632B0FC1B0}">
+    <comment ref="AB8" authorId="0" shapeId="0" xr:uid="{C81C0957-4AA8-2C44-9B2A-21632B0FC1B0}">
       <text>
         <r>
           <rPr>
@@ -549,7 +549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{2DA2560A-D047-314B-87CD-D1AF1417209B}">
+    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{2DA2560A-D047-314B-87CD-D1AF1417209B}">
       <text>
         <r>
           <rPr>
@@ -563,7 +563,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{2A92D54C-2237-B647-AE25-A2ABE361121C}">
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{2A92D54C-2237-B647-AE25-A2ABE361121C}">
       <text>
         <r>
           <rPr>
@@ -577,7 +577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{717E4CFF-DDBA-2F4F-9190-18A3F2F4112F}">
+    <comment ref="K9" authorId="0" shapeId="0" xr:uid="{717E4CFF-DDBA-2F4F-9190-18A3F2F4112F}">
       <text>
         <r>
           <rPr>
@@ -591,7 +591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{BCEF6DC5-CE6A-7248-8945-DFEB52F1BA33}">
+    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{BCEF6DC5-CE6A-7248-8945-DFEB52F1BA33}">
       <text>
         <r>
           <rPr>
@@ -605,7 +605,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{56AE115F-A126-084F-B077-07EA5D947906}">
+    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{56AE115F-A126-084F-B077-07EA5D947906}">
       <text>
         <r>
           <rPr>
@@ -619,7 +619,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{339FBB8E-E07D-B840-98EC-C80B64B927CB}">
+    <comment ref="O9" authorId="0" shapeId="0" xr:uid="{339FBB8E-E07D-B840-98EC-C80B64B927CB}">
       <text>
         <r>
           <rPr>
@@ -633,7 +633,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S9" authorId="0" shapeId="0" xr:uid="{46EE61CB-8DEA-B34D-B46C-61C9F3B2F7D8}">
+    <comment ref="T9" authorId="0" shapeId="0" xr:uid="{46EE61CB-8DEA-B34D-B46C-61C9F3B2F7D8}">
       <text>
         <r>
           <rPr>
@@ -647,7 +647,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W9" authorId="0" shapeId="0" xr:uid="{96252001-53A7-2D47-B105-8621CFC439F9}">
+    <comment ref="X9" authorId="0" shapeId="0" xr:uid="{96252001-53A7-2D47-B105-8621CFC439F9}">
       <text>
         <r>
           <rPr>
@@ -661,7 +661,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y9" authorId="0" shapeId="0" xr:uid="{452F243B-B589-6148-A36E-B2917CE3CD92}">
+    <comment ref="Z9" authorId="0" shapeId="0" xr:uid="{452F243B-B589-6148-A36E-B2917CE3CD92}">
       <text>
         <r>
           <rPr>
@@ -675,7 +675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA9" authorId="0" shapeId="0" xr:uid="{5A7E6893-A99C-1343-AB58-35F3E469ABE8}">
+    <comment ref="AB9" authorId="0" shapeId="0" xr:uid="{5A7E6893-A99C-1343-AB58-35F3E469ABE8}">
       <text>
         <r>
           <rPr>
@@ -689,7 +689,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{09655BB5-F296-2F40-97E2-A5805C2282FE}">
+    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{09655BB5-F296-2F40-97E2-A5805C2282FE}">
       <text>
         <r>
           <rPr>
@@ -703,7 +703,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{E8E8D432-E538-5D48-8012-954B776EFCCC}">
+    <comment ref="O10" authorId="0" shapeId="0" xr:uid="{E8E8D432-E538-5D48-8012-954B776EFCCC}">
       <text>
         <r>
           <rPr>
@@ -717,7 +717,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P10" authorId="0" shapeId="0" xr:uid="{C49A1688-FB91-0D49-A045-1CCA5B9F9536}">
+    <comment ref="Q10" authorId="0" shapeId="0" xr:uid="{C49A1688-FB91-0D49-A045-1CCA5B9F9536}">
       <text>
         <r>
           <rPr>
@@ -731,7 +731,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X10" authorId="0" shapeId="0" xr:uid="{C7E224C5-EB8B-684D-A9EC-6AB3218ED082}">
+    <comment ref="Y10" authorId="0" shapeId="0" xr:uid="{C7E224C5-EB8B-684D-A9EC-6AB3218ED082}">
       <text>
         <r>
           <rPr>
@@ -745,7 +745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA10" authorId="0" shapeId="0" xr:uid="{C74A0A0E-D3D4-BA45-B13D-E5BFE7DCDB4A}">
+    <comment ref="AB10" authorId="0" shapeId="0" xr:uid="{C74A0A0E-D3D4-BA45-B13D-E5BFE7DCDB4A}">
       <text>
         <r>
           <rPr>
@@ -759,7 +759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P12" authorId="0" shapeId="0" xr:uid="{71A6A668-7BDA-B347-8211-B950F8A3A6AE}">
+    <comment ref="Q12" authorId="0" shapeId="0" xr:uid="{71A6A668-7BDA-B347-8211-B950F8A3A6AE}">
       <text>
         <r>
           <rPr>
@@ -773,7 +773,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W12" authorId="0" shapeId="0" xr:uid="{2ADA8ABC-7E55-B845-AE66-5F59FB241FC4}">
+    <comment ref="X12" authorId="0" shapeId="0" xr:uid="{2ADA8ABC-7E55-B845-AE66-5F59FB241FC4}">
       <text>
         <r>
           <rPr>
@@ -787,7 +787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P13" authorId="0" shapeId="0" xr:uid="{13CDD3FB-F2A8-464E-A2B9-060761789508}">
+    <comment ref="Q13" authorId="0" shapeId="0" xr:uid="{13CDD3FB-F2A8-464E-A2B9-060761789508}">
       <text>
         <r>
           <rPr>
@@ -801,7 +801,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0" xr:uid="{28C333F1-90A8-AF42-9BE0-ED0158DAE426}">
+    <comment ref="Y16" authorId="0" shapeId="0" xr:uid="{28C333F1-90A8-AF42-9BE0-ED0158DAE426}">
       <text>
         <r>
           <rPr>
@@ -815,7 +815,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y16" authorId="0" shapeId="0" xr:uid="{6761C6F8-75CF-214B-97F0-E2144C456141}">
+    <comment ref="Z16" authorId="0" shapeId="0" xr:uid="{6761C6F8-75CF-214B-97F0-E2144C456141}">
       <text>
         <r>
           <rPr>
@@ -829,7 +829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA16" authorId="0" shapeId="0" xr:uid="{BDE3B640-8BA9-214C-8612-584B112C3C84}">
+    <comment ref="AB16" authorId="0" shapeId="0" xr:uid="{BDE3B640-8BA9-214C-8612-584B112C3C84}">
       <text>
         <r>
           <rPr>
@@ -843,7 +843,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0" xr:uid="{32153822-2D42-6944-8CA0-1E058EEC094D}">
+    <comment ref="N17" authorId="0" shapeId="0" xr:uid="{32153822-2D42-6944-8CA0-1E058EEC094D}">
       <text>
         <r>
           <rPr>
@@ -857,7 +857,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W17" authorId="0" shapeId="0" xr:uid="{5E86B897-0A10-EC40-BC49-7630CC24D132}">
+    <comment ref="X17" authorId="0" shapeId="0" xr:uid="{5E86B897-0A10-EC40-BC49-7630CC24D132}">
       <text>
         <r>
           <rPr>
@@ -871,7 +871,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X17" authorId="0" shapeId="0" xr:uid="{0A475759-5A7A-994C-AE85-AF0207770C7A}">
+    <comment ref="Y17" authorId="0" shapeId="0" xr:uid="{0A475759-5A7A-994C-AE85-AF0207770C7A}">
       <text>
         <r>
           <rPr>
@@ -885,7 +885,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{A07C86AC-DCC8-9749-82C5-C7322F0E4744}">
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{A07C86AC-DCC8-9749-82C5-C7322F0E4744}">
       <text>
         <r>
           <rPr>
@@ -899,7 +899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X21" authorId="0" shapeId="0" xr:uid="{DC873673-D92E-BD47-8E3B-833323746739}">
+    <comment ref="Y21" authorId="0" shapeId="0" xr:uid="{DC873673-D92E-BD47-8E3B-833323746739}">
       <text>
         <r>
           <rPr>
@@ -918,7 +918,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="102">
   <si>
     <r>
       <rPr>
@@ -1401,12 +1401,15 @@
   <si>
     <t>Ezeiza</t>
   </si>
+  <si>
+    <t>carnet</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1466,6 +1469,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1582,7 +1593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1619,13 +1630,19 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4132,14 +4149,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="4" width="16" customWidth="1"/>
-    <col min="5" max="28" width="9" customWidth="1"/>
+    <col min="1" max="5" width="16" customWidth="1"/>
+    <col min="6" max="29" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -4147,7 +4164,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -4155,152 +4172,162 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.15">
-      <c r="A5" s="20" t="s">
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A5" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="26"/>
+      <c r="H5" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="26"/>
+      <c r="J5" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20" t="s">
+      <c r="M5" s="26"/>
+      <c r="N5" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20" t="s">
+      <c r="O5" s="26"/>
+      <c r="P5" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20" t="s">
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20" t="s">
+      <c r="S5" s="26"/>
+      <c r="T5" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20" t="s">
+      <c r="U5" s="26"/>
+      <c r="V5" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20" t="s">
+      <c r="W5" s="26"/>
+      <c r="X5" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20" t="s">
+      <c r="Y5" s="26"/>
+      <c r="Z5" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20" t="s">
+      <c r="AA5" s="26"/>
+      <c r="AB5" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="AB5" s="20"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.15">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19" t="s">
+      <c r="AC5" s="26"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="G6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="H6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="I6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="J6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="K6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="L6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="M6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="M6" s="19" t="s">
+      <c r="N6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="N6" s="19" t="s">
+      <c r="O6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="O6" s="19" t="s">
+      <c r="P6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="P6" s="19" t="s">
+      <c r="Q6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="Q6" s="19" t="s">
+      <c r="R6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="R6" s="19" t="s">
+      <c r="S6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="S6" s="19" t="s">
+      <c r="T6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="T6" s="19" t="s">
+      <c r="U6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="U6" s="19" t="s">
+      <c r="V6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="V6" s="19" t="s">
+      <c r="W6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="W6" s="19" t="s">
+      <c r="X6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="X6" s="19" t="s">
+      <c r="Y6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="Y6" s="19" t="s">
+      <c r="Z6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="Z6" s="19" t="s">
+      <c r="AA6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="AA6" s="19" t="s">
+      <c r="AB6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="AB6" s="19" t="s">
+      <c r="AC6" s="19" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
       <c r="B7" t="s">
         <v>66</v>
       </c>
@@ -4310,31 +4337,39 @@
       <c r="D7">
         <v>28410856</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20241120090</t>
+        </is>
+      </c>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22">
         <v>2</v>
       </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23">
+      <c r="J7" s="22"/>
+      <c r="K7" s="22">
         <v>1</v>
       </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="AA7" s="23"/>
-    </row>
-    <row r="8" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="22"/>
+      <c r="AB7" s="22"/>
+    </row>
+    <row r="8" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2</v>
+      </c>
       <c r="B8" t="s">
         <v>68</v>
       </c>
@@ -4344,39 +4379,47 @@
       <c r="D8">
         <v>30911705</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20241110589</t>
+        </is>
+      </c>
+      <c r="F8" s="23">
         <v>2</v>
       </c>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="I8" s="26">
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="J8" s="25">
         <v>1</v>
       </c>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24" t="s">
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24">
+      <c r="N8" s="23"/>
+      <c r="O8" s="23">
         <v>2</v>
       </c>
-      <c r="P8" s="24">
+      <c r="Q8" s="23">
         <v>2</v>
       </c>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="AA8" s="24">
+      <c r="S8" s="23"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="23"/>
+      <c r="Z8" s="23"/>
+      <c r="AB8" s="23">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>3</v>
+      </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
@@ -4386,53 +4429,56 @@
       <c r="D9">
         <v>30394726</v>
       </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="25">
+      <c r="F9" s="22"/>
+      <c r="G9" s="24">
         <v>8</v>
       </c>
-      <c r="G9" s="23">
+      <c r="H9" s="22">
         <v>4</v>
       </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25">
+      <c r="J9" s="24"/>
+      <c r="K9" s="24">
         <v>4</v>
       </c>
-      <c r="K9" s="25">
+      <c r="L9" s="24">
         <v>1</v>
       </c>
-      <c r="L9" s="25">
+      <c r="M9" s="24">
         <v>5</v>
       </c>
-      <c r="M9" s="25">
+      <c r="N9" s="24">
         <v>4</v>
       </c>
-      <c r="N9" s="25">
+      <c r="O9" s="24">
         <v>4</v>
       </c>
-      <c r="P9" s="23"/>
-      <c r="R9" s="23">
+      <c r="Q9" s="22"/>
+      <c r="S9" s="22">
         <v>1</v>
       </c>
-      <c r="S9" s="25">
+      <c r="T9" s="24">
         <v>3</v>
       </c>
-      <c r="T9" s="25">
+      <c r="U9" s="24">
         <v>1</v>
       </c>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="25">
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="24">
         <v>4</v>
       </c>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25">
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24">
         <v>4</v>
       </c>
-      <c r="AA9" s="25">
+      <c r="AB9" s="24">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>4</v>
+      </c>
       <c r="B10" t="s">
         <v>72</v>
       </c>
@@ -4442,43 +4488,51 @@
       <c r="D10">
         <v>32333927</v>
       </c>
-      <c r="E10" s="24"/>
-      <c r="F10" s="26">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20251120107</t>
+        </is>
+      </c>
+      <c r="F10" s="23"/>
+      <c r="G10" s="25">
         <v>1</v>
       </c>
-      <c r="G10" s="26">
+      <c r="H10" s="25">
         <v>3</v>
       </c>
-      <c r="I10" s="26">
+      <c r="J10" s="25">
         <v>1</v>
       </c>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24">
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23">
         <v>2</v>
       </c>
-      <c r="P10" s="24">
+      <c r="Q10" s="23">
         <v>2</v>
       </c>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24">
+      <c r="S10" s="23"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="23"/>
+      <c r="V10" s="23"/>
+      <c r="W10" s="23">
         <v>1</v>
       </c>
-      <c r="W10" s="22"/>
-      <c r="X10" s="24">
+      <c r="X10" s="21"/>
+      <c r="Y10" s="23">
         <v>2</v>
       </c>
-      <c r="Y10" s="24"/>
-      <c r="AA10" s="24">
+      <c r="Z10" s="23"/>
+      <c r="AB10" s="23">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>5</v>
+      </c>
       <c r="B11" t="s">
         <v>74</v>
       </c>
@@ -4488,27 +4542,35 @@
       <c r="D11">
         <v>31464995</v>
       </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
-      <c r="AA11" s="23"/>
-    </row>
-    <row r="12" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20251110145</t>
+        </is>
+      </c>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AB11" s="22"/>
+    </row>
+    <row r="12" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>6</v>
+      </c>
       <c r="B12" t="s">
         <v>66</v>
       </c>
@@ -4518,33 +4580,36 @@
       <c r="D12">
         <v>31042821</v>
       </c>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="P12" s="24">
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="Q12" s="23">
         <v>2</v>
       </c>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24">
+      <c r="S12" s="23"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23">
         <v>1</v>
       </c>
-      <c r="V12" s="22"/>
-      <c r="W12" s="24">
+      <c r="W12" s="21"/>
+      <c r="X12" s="23">
         <v>5</v>
       </c>
-      <c r="X12" s="24"/>
-      <c r="Y12" s="24"/>
-      <c r="AA12" s="24"/>
-    </row>
-    <row r="13" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
+      <c r="AB12" s="23"/>
+    </row>
+    <row r="13" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>7</v>
+      </c>
       <c r="B13" t="s">
         <v>77</v>
       </c>
@@ -4554,29 +4619,37 @@
       <c r="D13">
         <v>29724329</v>
       </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="P13" s="25">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>20221110604</t>
+        </is>
+      </c>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="Q13" s="24">
         <v>4</v>
       </c>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="AA13" s="23"/>
-    </row>
-    <row r="14" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AB13" s="22"/>
+    </row>
+    <row r="14" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>8</v>
+      </c>
       <c r="B14" t="s">
         <v>79</v>
       </c>
@@ -4586,27 +4659,35 @@
       <c r="D14">
         <v>31785756</v>
       </c>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="AA14" s="24"/>
-    </row>
-    <row r="15" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>20241130167</t>
+        </is>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
+      <c r="AB14" s="23"/>
+    </row>
+    <row r="15" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>9</v>
+      </c>
       <c r="B15" t="s">
         <v>81</v>
       </c>
@@ -4616,27 +4697,35 @@
       <c r="D15">
         <v>31985434</v>
       </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
-      <c r="AA15" s="23"/>
-    </row>
-    <row r="16" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>20251110305</t>
+        </is>
+      </c>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AB15" s="22"/>
+    </row>
+    <row r="16" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>10</v>
+      </c>
       <c r="B16" t="s">
         <v>83</v>
       </c>
@@ -4646,35 +4735,38 @@
       <c r="D16">
         <v>31758845</v>
       </c>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24">
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23">
         <v>1</v>
       </c>
-      <c r="W16" s="24"/>
-      <c r="X16" s="26">
+      <c r="X16" s="23"/>
+      <c r="Y16" s="25">
         <v>4</v>
       </c>
-      <c r="Y16" s="24">
+      <c r="Z16" s="23">
         <v>2</v>
       </c>
-      <c r="AA16" s="24">
+      <c r="AB16" s="23">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>11</v>
+      </c>
       <c r="B17" t="s">
         <v>85</v>
       </c>
@@ -4684,71 +4776,81 @@
       <c r="D17">
         <v>31377369</v>
       </c>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="25">
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="24">
         <v>3</v>
       </c>
-      <c r="N17" s="23">
+      <c r="O17" s="22">
         <v>1</v>
       </c>
-      <c r="P17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="25">
+      <c r="Q17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="24">
         <v>1</v>
       </c>
-      <c r="W17" s="23">
+      <c r="X17" s="22">
         <v>2</v>
       </c>
-      <c r="X17" s="23">
+      <c r="Y17" s="22">
         <v>2</v>
       </c>
-      <c r="Y17" s="23"/>
-      <c r="AA17" s="23"/>
-    </row>
-    <row r="18" spans="2:27" ht="15" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>88</v>
+      <c r="Z17" s="22"/>
+      <c r="AB17" s="22"/>
+    </row>
+    <row r="18" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alirio</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ugarte</t>
+        </is>
       </c>
       <c r="D18">
         <v>32377039</v>
       </c>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24">
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23">
         <v>2</v>
       </c>
-      <c r="I18" s="26">
+      <c r="J18" s="25">
         <v>1</v>
       </c>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="24"/>
-      <c r="Y18" s="24"/>
-      <c r="AA18" s="24"/>
-    </row>
-    <row r="19" spans="2:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
+      <c r="W18" s="23"/>
+      <c r="X18" s="23"/>
+      <c r="Y18" s="23"/>
+      <c r="Z18" s="23"/>
+      <c r="AB18" s="23"/>
+    </row>
+    <row r="19" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>13</v>
+      </c>
       <c r="B19" t="s">
         <v>89</v>
       </c>
@@ -4758,27 +4860,35 @@
       <c r="D19">
         <v>32124905</v>
       </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="23"/>
-      <c r="AA19" s="23"/>
-    </row>
-    <row r="20" spans="2:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>20251130008</t>
+        </is>
+      </c>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="22"/>
+      <c r="V19" s="22"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="22"/>
+      <c r="Y19" s="22"/>
+      <c r="Z19" s="22"/>
+      <c r="AB19" s="22"/>
+    </row>
+    <row r="20" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>14</v>
+      </c>
       <c r="B20" t="s">
         <v>91</v>
       </c>
@@ -4788,27 +4898,35 @@
       <c r="D20">
         <v>24843496</v>
       </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="AA20" s="24"/>
-    </row>
-    <row r="21" spans="2:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>20221120086</t>
+        </is>
+      </c>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="S20" s="23"/>
+      <c r="T20" s="23"/>
+      <c r="U20" s="23"/>
+      <c r="V20" s="23"/>
+      <c r="W20" s="23"/>
+      <c r="X20" s="23"/>
+      <c r="Y20" s="23"/>
+      <c r="Z20" s="23"/>
+      <c r="AB20" s="23"/>
+    </row>
+    <row r="21" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>15</v>
+      </c>
       <c r="B21" t="s">
         <v>93</v>
       </c>
@@ -4818,35 +4936,43 @@
       <c r="D21">
         <v>30538925</v>
       </c>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>20251120012</t>
+        </is>
+      </c>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22">
         <v>1</v>
       </c>
-      <c r="I21" s="23">
+      <c r="J21" s="22">
         <v>1</v>
       </c>
-      <c r="J21" s="21"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="25">
+      <c r="K21" s="20"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="24">
         <v>1</v>
       </c>
-      <c r="N21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="25">
+      <c r="O21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="S21" s="22"/>
+      <c r="T21" s="22"/>
+      <c r="U21" s="22"/>
+      <c r="V21" s="22"/>
+      <c r="W21" s="22"/>
+      <c r="X21" s="22"/>
+      <c r="Y21" s="24">
         <v>4</v>
       </c>
-      <c r="Y21" s="23"/>
-      <c r="AA21" s="23"/>
-    </row>
-    <row r="22" spans="2:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="Z21" s="22"/>
+      <c r="AB21" s="22"/>
+    </row>
+    <row r="22" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>16</v>
+      </c>
       <c r="B22" t="s">
         <v>95</v>
       </c>
@@ -4856,27 +4982,35 @@
       <c r="D22">
         <v>31707262</v>
       </c>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="24"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="24"/>
-      <c r="X22" s="24"/>
-      <c r="Y22" s="24"/>
-      <c r="AA22" s="24"/>
-    </row>
-    <row r="23" spans="2:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>20251110309</t>
+        </is>
+      </c>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="W22" s="23"/>
+      <c r="X22" s="23"/>
+      <c r="Y22" s="23"/>
+      <c r="Z22" s="23"/>
+      <c r="AB22" s="23"/>
+    </row>
+    <row r="23" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>17</v>
+      </c>
       <c r="B23" t="s">
         <v>97</v>
       </c>
@@ -4886,27 +5020,35 @@
       <c r="D23">
         <v>31307971</v>
       </c>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="23"/>
-      <c r="AA23" s="23"/>
-    </row>
-    <row r="24" spans="2:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>20241110377</t>
+        </is>
+      </c>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="Q23" s="22"/>
+      <c r="S23" s="22"/>
+      <c r="T23" s="22"/>
+      <c r="U23" s="22"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="22"/>
+      <c r="X23" s="22"/>
+      <c r="Y23" s="22"/>
+      <c r="Z23" s="22"/>
+      <c r="AB23" s="22"/>
+    </row>
+    <row r="24" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>18</v>
+      </c>
       <c r="B24" t="s">
         <v>99</v>
       </c>
@@ -4916,48 +5058,49 @@
       <c r="D24">
         <v>31707260</v>
       </c>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="26">
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="25">
         <v>1</v>
       </c>
-      <c r="U24" s="24">
+      <c r="V24" s="23">
         <v>1</v>
       </c>
-      <c r="V24" s="22"/>
-      <c r="W24" s="24"/>
-      <c r="X24" s="24"/>
-      <c r="Y24" s="24"/>
-      <c r="AA24" s="24"/>
+      <c r="W24" s="21"/>
+      <c r="X24" s="23"/>
+      <c r="Y24" s="23"/>
+      <c r="Z24" s="23"/>
+      <c r="AB24" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
+  <mergeCells count="17">
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/Datos Tesis Upstream/Estructura de Datos/2526-2/Participaciones ESTRUCTURAS DE DATOS - Enero-Marzo 2526-2.xlsx
+++ b/Datos Tesis Upstream/Estructura de Datos/2526-2/Participaciones ESTRUCTURAS DE DATOS - Enero-Marzo 2526-2.xlsx
@@ -15,6 +15,7 @@
   <sheets>
     <sheet name="ESTRUCTURAS-DE DATOS" sheetId="1" r:id="rId1"/>
     <sheet name="Estandar" sheetId="2" r:id="rId2"/>
+    <sheet name="Cronograma" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4421,190 +4422,196 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D9">
-        <v>30394726</v>
+        <v>31985434</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20251110305</t>
+        </is>
       </c>
       <c r="F9" s="22"/>
-      <c r="G9" s="24">
-        <v>8</v>
-      </c>
-      <c r="H9" s="22">
-        <v>4</v>
-      </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24">
-        <v>4</v>
-      </c>
-      <c r="L9" s="24">
-        <v>1</v>
-      </c>
-      <c r="M9" s="24">
-        <v>5</v>
-      </c>
-      <c r="N9" s="24">
-        <v>4</v>
-      </c>
-      <c r="O9" s="24">
-        <v>4</v>
-      </c>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
       <c r="Q9" s="22"/>
-      <c r="S9" s="22">
-        <v>1</v>
-      </c>
-      <c r="T9" s="24">
-        <v>3</v>
-      </c>
-      <c r="U9" s="24">
-        <v>1</v>
-      </c>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
       <c r="V9" s="22"/>
       <c r="W9" s="22"/>
-      <c r="X9" s="24">
-        <v>4</v>
-      </c>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="24">
-        <v>4</v>
-      </c>
-      <c r="AB9" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="X9" s="22"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="22"/>
+      <c r="AB9" s="22"/>
+    </row>
+    <row r="10" spans="1:28" ht="15" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="D10">
-        <v>32333927</v>
+        <v>30538925</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20251120107</t>
+          <t>20251120012</t>
         </is>
       </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="25">
-        <v>1</v>
-      </c>
-      <c r="H10" s="25">
-        <v>3</v>
-      </c>
-      <c r="J10" s="25">
-        <v>1</v>
-      </c>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="23">
-        <v>2</v>
-      </c>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23">
-        <v>1</v>
-      </c>
-      <c r="X10" s="21"/>
-      <c r="Y10" s="23">
-        <v>2</v>
-      </c>
-      <c r="Z10" s="23"/>
-      <c r="AB10" s="23">
-        <v>2</v>
-      </c>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22">
+        <v>1</v>
+      </c>
+      <c r="J10" s="22">
+        <v>1</v>
+      </c>
+      <c r="K10" s="20"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="24">
+        <v>1</v>
+      </c>
+      <c r="O10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="24">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="22"/>
+      <c r="AB10" s="22"/>
     </row>
     <row r="11" spans="1:29" ht="15" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D11">
-        <v>31464995</v>
+        <v>30394726</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20251110145</t>
+          <t>2022</t>
         </is>
       </c>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="24">
+        <v>8</v>
+      </c>
+      <c r="H11" s="22">
+        <v>4</v>
+      </c>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24">
+        <v>4</v>
+      </c>
+      <c r="L11" s="24">
+        <v>1</v>
+      </c>
+      <c r="M11" s="24">
+        <v>5</v>
+      </c>
+      <c r="N11" s="24">
+        <v>4</v>
+      </c>
+      <c r="O11" s="24">
+        <v>4</v>
+      </c>
       <c r="Q11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
+      <c r="S11" s="22">
+        <v>1</v>
+      </c>
+      <c r="T11" s="24">
+        <v>3</v>
+      </c>
+      <c r="U11" s="24">
+        <v>1</v>
+      </c>
       <c r="V11" s="22"/>
       <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-      <c r="AB11" s="22"/>
-    </row>
-    <row r="12" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+      <c r="X11" s="24">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="24"/>
+      <c r="Z11" s="24">
+        <v>4</v>
+      </c>
+      <c r="AB11" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="15" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D12">
-        <v>31042821</v>
-      </c>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="Q12" s="23">
+        <v>31377369</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="24">
+        <v>3</v>
+      </c>
+      <c r="O12" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="24">
+        <v>1</v>
+      </c>
+      <c r="X12" s="22">
         <v>2</v>
       </c>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23">
-        <v>1</v>
-      </c>
-      <c r="W12" s="21"/>
-      <c r="X12" s="23">
-        <v>5</v>
-      </c>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="23"/>
-      <c r="AB12" s="23"/>
+      <c r="Y12" s="22">
+        <v>2</v>
+      </c>
+      <c r="Z12" s="22"/>
+      <c r="AB12" s="22"/>
     </row>
     <row r="13" spans="1:29" ht="15" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -4646,22 +4653,22 @@
       <c r="Z13" s="22"/>
       <c r="AB13" s="22"/>
     </row>
-    <row r="14" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" ht="15" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D14">
-        <v>31785756</v>
+        <v>31707260</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20241130167</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F14" s="23"/>
@@ -4676,30 +4683,34 @@
       <c r="Q14" s="23"/>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
+      <c r="U14" s="25">
+        <v>1</v>
+      </c>
+      <c r="V14" s="23">
+        <v>1</v>
+      </c>
+      <c r="W14" s="21"/>
       <c r="X14" s="23"/>
       <c r="Y14" s="23"/>
       <c r="Z14" s="23"/>
       <c r="AB14" s="23"/>
     </row>
-    <row r="15" spans="1:29" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" ht="15" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D15">
-        <v>31985434</v>
+        <v>31307971</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20251110305</t>
+          <t>20241110377</t>
         </is>
       </c>
       <c r="F15" s="22"/>
@@ -4735,6 +4746,11 @@
       <c r="D16">
         <v>31758845</v>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
@@ -4768,69 +4784,61 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D17">
-        <v>31377369</v>
-      </c>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="24">
-        <v>3</v>
-      </c>
-      <c r="O17" s="22">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="24">
-        <v>1</v>
-      </c>
-      <c r="X17" s="22">
-        <v>2</v>
-      </c>
-      <c r="Y17" s="22">
-        <v>2</v>
-      </c>
-      <c r="Z17" s="22"/>
-      <c r="AB17" s="22"/>
-    </row>
-    <row r="18" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+        <v>24843496</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>20221120086</t>
+        </is>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="23"/>
+      <c r="AB17" s="23"/>
+    </row>
+    <row r="18" spans="1:29" ht="15" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>12</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18">
+        <v>31785756</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
-          <t>Alirio</t>
+          <t>20241130167</t>
         </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ugarte</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>32377039</v>
       </c>
       <c r="F18" s="23"/>
       <c r="G18" s="23"/>
-      <c r="H18" s="23">
-        <v>2</v>
-      </c>
-      <c r="J18" s="25">
-        <v>1</v>
-      </c>
+      <c r="H18" s="23"/>
+      <c r="J18" s="23"/>
       <c r="K18" s="23"/>
       <c r="L18" s="23"/>
       <c r="M18" s="23"/>
@@ -4847,27 +4855,27 @@
       <c r="Z18" s="23"/>
       <c r="AB18" s="23"/>
     </row>
-    <row r="19" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="15" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D19">
-        <v>32124905</v>
+        <v>31464995</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20251130008</t>
+          <t>20251110145</t>
         </is>
       </c>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
       <c r="J19" s="22"/>
       <c r="K19" s="22"/>
       <c r="L19" s="22"/>
@@ -4890,107 +4898,123 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D20">
-        <v>24843496</v>
+        <v>32124905</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20221120086</t>
+          <t>20251130008</t>
         </is>
       </c>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="23"/>
-      <c r="X20" s="23"/>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="23"/>
-      <c r="AB20" s="23"/>
-    </row>
-    <row r="21" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="22"/>
+      <c r="Y20" s="22"/>
+      <c r="Z20" s="22"/>
+      <c r="AB20" s="22"/>
+    </row>
+    <row r="21" spans="1:29" ht="15" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D21">
-        <v>30538925</v>
+        <v>32333927</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20251120012</t>
+          <t>20251120107</t>
         </is>
       </c>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22">
-        <v>1</v>
-      </c>
-      <c r="J21" s="22">
-        <v>1</v>
-      </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="24">
-        <v>1</v>
-      </c>
-      <c r="O21" s="22"/>
-      <c r="Q21" s="22"/>
-      <c r="S21" s="22"/>
-      <c r="T21" s="22"/>
-      <c r="U21" s="22"/>
-      <c r="V21" s="22"/>
-      <c r="W21" s="22"/>
-      <c r="X21" s="22"/>
-      <c r="Y21" s="24">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="22"/>
-      <c r="AB21" s="22"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="25">
+        <v>1</v>
+      </c>
+      <c r="H21" s="25">
+        <v>3</v>
+      </c>
+      <c r="J21" s="25">
+        <v>1</v>
+      </c>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="23">
+        <v>2</v>
+      </c>
+      <c r="S21" s="23"/>
+      <c r="T21" s="23"/>
+      <c r="U21" s="23"/>
+      <c r="V21" s="23"/>
+      <c r="W21" s="23">
+        <v>1</v>
+      </c>
+      <c r="X21" s="21"/>
+      <c r="Y21" s="23">
+        <v>2</v>
+      </c>
+      <c r="Z21" s="23"/>
+      <c r="AB21" s="23">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" spans="1:28" ht="15" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>16</v>
       </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>96</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alirio</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ugarte</t>
+        </is>
       </c>
       <c r="D22">
-        <v>31707262</v>
+        <v>32377039</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20251110309</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F22" s="23"/>
       <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="J22" s="23"/>
+      <c r="H22" s="23">
+        <v>2</v>
+      </c>
+      <c r="J22" s="25">
+        <v>1</v>
+      </c>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
       <c r="M22" s="23"/>
@@ -5007,56 +5031,67 @@
       <c r="Z22" s="23"/>
       <c r="AB22" s="23"/>
     </row>
-    <row r="23" spans="1:28" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="15" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D23">
-        <v>31307971</v>
+        <v>31042821</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20241110377</t>
+          <t>2024</t>
         </is>
       </c>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="Q23" s="22"/>
-      <c r="S23" s="22"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="22"/>
-      <c r="X23" s="22"/>
-      <c r="Y23" s="22"/>
-      <c r="Z23" s="22"/>
-      <c r="AB23" s="22"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="Q23" s="23">
+        <v>2</v>
+      </c>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23">
+        <v>1</v>
+      </c>
+      <c r="W23" s="21"/>
+      <c r="X23" s="23">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="23"/>
+      <c r="Z23" s="23"/>
+      <c r="AB23" s="23"/>
     </row>
     <row r="24" spans="1:28" ht="15" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D24">
-        <v>31707260</v>
+        <v>31707262</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>20251110309</t>
+        </is>
       </c>
       <c r="F24" s="23"/>
       <c r="G24" s="23"/>
@@ -5070,13 +5105,9 @@
       <c r="Q24" s="23"/>
       <c r="S24" s="23"/>
       <c r="T24" s="23"/>
-      <c r="U24" s="25">
-        <v>1</v>
-      </c>
-      <c r="V24" s="23">
-        <v>1</v>
-      </c>
-      <c r="W24" s="21"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="23"/>
+      <c r="W24" s="23"/>
       <c r="X24" s="23"/>
       <c r="Y24" s="23"/>
       <c r="Z24" s="23"/>
@@ -5105,4 +5136,335 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>